--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260630.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260630.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr"/>
@@ -975,10 +975,14 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr"/>
+          <t>Zuellig Pharma</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>088-423500</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1165,7 +1169,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr"/>
@@ -1325,7 +1329,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1789,7 +1793,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr"/>
@@ -2397,7 +2401,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2477,7 +2481,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr"/>
@@ -2566,7 +2570,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-30 14:00</t>
+          <t>Generated: 2026-06-30 16:06</t>
         </is>
       </c>
     </row>
